--- a/Team-Data/2008-09/3-13-2008-09.xlsx
+++ b/Team-Data/2008-09/3-13-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,85 +728,85 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
         <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O2" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P2" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V2" t="n">
         <v>12.8</v>
       </c>
       <c r="W2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X2" t="n">
         <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB2" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,13 +836,13 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -784,22 +851,22 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU2" t="n">
         <v>19</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -864,64 +931,64 @@
         <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AA3" t="n">
         <v>22.7</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>22.6</v>
-      </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -954,13 +1021,13 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
@@ -972,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.431</v>
+        <v>0.438</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1046,7 +1113,7 @@
         <v>76.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1055,16 +1122,16 @@
         <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
@@ -1097,25 +1164,25 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1145,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1160,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1210,49 +1277,49 @@
         <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.431</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
         <v>42.7</v>
@@ -1261,31 +1328,31 @@
         <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1303,13 +1370,13 @@
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
         <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
@@ -1318,10 +1385,10 @@
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,13 +1406,13 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1392,49 +1459,49 @@
         <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="H6" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.755</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>41.6</v>
@@ -1443,49 +1510,49 @@
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
         <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.6</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1494,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>2</v>
@@ -1503,7 +1570,7 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
@@ -1518,10 +1585,10 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1533,10 +1600,10 @@
         <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.606</v>
+        <v>0.615</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="K7" t="n">
         <v>0.461</v>
@@ -1598,19 +1665,19 @@
         <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N7" t="n">
         <v>0.346</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.82</v>
+        <v>0.821</v>
       </c>
       <c r="R7" t="n">
         <v>11.2</v>
@@ -1619,10 +1686,10 @@
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
         <v>13.2</v>
@@ -1631,37 +1698,37 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>19.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1670,13 +1737,13 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN7" t="n">
         <v>25</v>
@@ -1691,25 +1758,25 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1843,10 +1910,10 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1876,7 +1943,7 @@
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1897,7 +1964,7 @@
         <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H9" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J9" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K9" t="n">
         <v>0.454</v>
@@ -1965,31 +2032,31 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P9" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0.751</v>
       </c>
       <c r="R9" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T9" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U9" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W9" t="n">
         <v>6.2</v>
@@ -2010,10 +2077,10 @@
         <v>93.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2025,13 +2092,13 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>17</v>
@@ -2043,7 +2110,7 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
@@ -2055,16 +2122,16 @@
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,10 +2140,10 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.344</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J10" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
@@ -2144,10 +2211,10 @@
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O10" t="n">
         <v>23.1</v>
@@ -2159,19 +2226,19 @@
         <v>0.784</v>
       </c>
       <c r="R10" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U10" t="n">
         <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>8</v>
@@ -2183,28 +2250,28 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
         <v>23.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
         <v>6</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
@@ -2234,22 +2301,22 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2261,7 +2328,7 @@
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.642</v>
+        <v>0.636</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,10 +2384,10 @@
         <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
         <v>7.7</v>
@@ -2329,31 +2396,31 @@
         <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S11" t="n">
         <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U11" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
         <v>6.9</v>
@@ -2365,25 +2432,25 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>21.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC11" t="n">
         <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>6</v>
@@ -2395,16 +2462,16 @@
         <v>25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
@@ -2419,16 +2486,16 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV11" t="n">
         <v>15</v>
@@ -2437,7 +2504,7 @@
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
         <v>24</v>
@@ -2449,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -2481,19 +2548,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I12" t="n">
         <v>38.9</v>
@@ -2502,22 +2569,22 @@
         <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O12" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0.8080000000000001</v>
@@ -2529,49 +2596,49 @@
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.5</v>
+        <v>104.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,22 +2647,22 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>3</v>
@@ -2616,7 +2683,7 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2625,16 +2692,16 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
         <v>27</v>
@@ -2768,7 +2835,7 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
         <v>23</v>
@@ -2798,7 +2865,7 @@
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2813,7 +2880,7 @@
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,40 +2930,40 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P14" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
         <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
         <v>13.5</v>
@@ -2914,28 +2981,28 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.5</v>
+        <v>108.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2947,22 +3014,22 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP14" t="n">
         <v>8</v>
       </c>
-      <c r="AP14" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2983,16 +3050,16 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3057,7 +3124,7 @@
         <v>13.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
@@ -3066,7 +3133,7 @@
         <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R15" t="n">
         <v>10.5</v>
@@ -3078,7 +3145,7 @@
         <v>39.1</v>
       </c>
       <c r="U15" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="V15" t="n">
         <v>15</v>
@@ -3102,22 +3169,22 @@
         <v>93.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3138,16 +3205,16 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3159,10 +3226,10 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3299,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3341,19 +3408,19 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
       </c>
       <c r="AX16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>4</v>
       </c>
-      <c r="AY16" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3412,40 +3479,40 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N17" t="n">
         <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3457,16 +3524,16 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,22 +3542,22 @@
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3499,16 +3566,16 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.292</v>
+        <v>0.297</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,7 +3658,7 @@
         <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.441</v>
@@ -3600,10 +3667,10 @@
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
         <v>19</v>
@@ -3624,34 +3691,34 @@
         <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y18" t="n">
         <v>6.4</v>
       </c>
-      <c r="X18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>6.3</v>
-      </c>
       <c r="Z18" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,13 +3730,13 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3678,16 +3745,16 @@
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -3699,25 +3766,25 @@
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
         <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.431</v>
+        <v>0.438</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3782,10 +3849,10 @@
         <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O19" t="n">
         <v>19.3</v>
@@ -3794,22 +3861,22 @@
         <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R19" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S19" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U19" t="n">
         <v>19.8</v>
       </c>
       <c r="V19" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W19" t="n">
         <v>7.1</v>
@@ -3818,10 +3885,10 @@
         <v>4.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
         <v>20.8</v>
@@ -3830,46 +3897,46 @@
         <v>98.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3881,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3893,19 +3960,19 @@
         <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.641</v>
+        <v>0.635</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3955,7 +4022,7 @@
         <v>35.3</v>
       </c>
       <c r="J20" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
@@ -3964,34 +4031,34 @@
         <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O20" t="n">
         <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S20" t="n">
         <v>30.1</v>
       </c>
       <c r="T20" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="U20" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W20" t="n">
         <v>7.3</v>
@@ -4000,10 +4067,10 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
         <v>20.9</v>
@@ -4012,13 +4079,13 @@
         <v>96.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
@@ -4027,7 +4094,7 @@
         <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,16 +4103,16 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
       </c>
       <c r="AM20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>22</v>
@@ -4066,13 +4133,13 @@
         <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
         <v>24</v>
@@ -4084,7 +4151,7 @@
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -4119,97 +4186,97 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.431</v>
+        <v>0.422</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J21" t="n">
         <v>86.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M21" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
         <v>20.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
         <v>106.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
@@ -4248,13 +4315,13 @@
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4412,10 +4479,10 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J23" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="O23" t="n">
         <v>20</v>
@@ -4522,46 +4589,46 @@
         <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
         <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V23" t="n">
         <v>14.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
         <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AC23" t="n">
         <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4594,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4621,7 +4688,7 @@
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J24" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="N24" t="n">
         <v>0.316</v>
       </c>
       <c r="O24" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P24" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q24" t="n">
         <v>0.74</v>
       </c>
       <c r="R24" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S24" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T24" t="n">
         <v>42.2</v>
       </c>
       <c r="U24" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V24" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W24" t="n">
         <v>8.1</v>
@@ -4734,10 +4801,10 @@
         <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0.5</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK24" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>13</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4788,13 +4855,13 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
         <v>18</v>
@@ -4806,10 +4873,10 @@
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
@@ -4976,7 +5043,7 @@
         <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4994,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5032,13 +5099,13 @@
         <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.641</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5047,37 +5114,37 @@
         <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
         <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5089,40 +5156,40 @@
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF26" t="n">
         <v>7</v>
       </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,19 +5222,19 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,13 +5243,13 @@
         <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.215</v>
+        <v>0.219</v>
       </c>
       <c r="H27" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M27" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P27" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.801</v>
@@ -5259,7 +5326,7 @@
         <v>28.9</v>
       </c>
       <c r="T27" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5271,25 +5338,25 @@
         <v>7</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>5</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,22 +5377,22 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5346,22 +5413,22 @@
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5534,7 +5601,7 @@
         <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H29" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I29" t="n">
         <v>36.6</v>
       </c>
       <c r="J29" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O29" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P29" t="n">
         <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
         <v>9</v>
@@ -5623,7 +5690,7 @@
         <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U29" t="n">
         <v>21.8</v>
@@ -5635,10 +5702,10 @@
         <v>6.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
         <v>19.4</v>
@@ -5653,31 +5720,31 @@
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM29" t="n">
         <v>23</v>
@@ -5686,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
         <v>28</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
@@ -5707,16 +5774,16 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
       </c>
       <c r="AF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG30" t="n">
         <v>8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>18</v>
@@ -5874,10 +5941,10 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>0.227</v>
+        <v>0.231</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,10 +6033,10 @@
         <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>0.328</v>
+        <v>0.325</v>
       </c>
       <c r="O31" t="n">
         <v>17.5</v>
@@ -5978,7 +6045,7 @@
         <v>22.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R31" t="n">
         <v>11.6</v>
@@ -5987,7 +6054,7 @@
         <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
         <v>20.2</v>
@@ -6011,13 +6078,13 @@
         <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC31" t="n">
         <v>-7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6056,10 +6123,10 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>30</v>
@@ -6077,7 +6144,7 @@
         <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>21</v>
@@ -6089,7 +6156,7 @@
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-13-2008-09</t>
+          <t>2009-03-13</t>
         </is>
       </c>
     </row>
